--- a/scripts/ground-truth/amalie-2026-02-27-cmf-2008.xlsx
+++ b/scripts/ground-truth/amalie-2026-02-27-cmf-2008.xlsx
@@ -3,6 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <bookViews>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
+  </bookViews>
   <sheets>
     <sheet sheetId="1" name="README" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Metadata" state="visible" r:id="rId5"/>
@@ -18,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="199">
   <si>
     <t>STIX Match Ground-Truth Tagger</t>
   </si>
@@ -125,7 +128,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27</t>
+    <t>2026-02-24</t>
   </si>
   <si>
     <t>YYYY-MM-DD</t>
@@ -155,15 +158,36 @@
     <t>My team color</t>
   </si>
   <si>
+    <t>Red</t>
+  </si>
+  <si>
     <t>Outfield jersey colour, lowercase</t>
   </si>
   <si>
     <t>Opponent color</t>
   </si>
   <si>
+    <t>Dark Blue / Black Stripes</t>
+  </si>
+  <si>
     <t>My GK color</t>
   </si>
   <si>
+    <t>Light Blue</t>
+  </si>
+  <si>
+    <t>Us GK sub at (MM:SS)</t>
+  </si>
+  <si>
+    <t>84:21</t>
+  </si>
+  <si>
+    <t>Opponent GK color</t>
+  </si>
+  <si>
+    <t>Light purple</t>
+  </si>
+  <si>
     <t>Age group</t>
   </si>
   <si>
@@ -185,7 +209,7 @@
     <t>video_job_id</t>
   </si>
   <si>
-    <t>d2df3782-65c9-4664-8593-4d2ceb89a699</t>
+    <t>c6e6c58b-c48b-4e99-8059-4dae0f976180</t>
   </si>
   <si>
     <t>Fill in after upload — needed for eval</t>
@@ -221,6 +245,51 @@
     <t>GK observations</t>
   </si>
   <si>
+    <t>86:23</t>
+  </si>
+  <si>
+    <t>Open play</t>
+  </si>
+  <si>
+    <t>Deflection</t>
+  </si>
+  <si>
+    <t>Central Box</t>
+  </si>
+  <si>
+    <t>Top</t>
+  </si>
+  <si>
+    <t>GK Left</t>
+  </si>
+  <si>
+    <t>Own goal. Defender tries to clear a cross but heads the ball high over the GK and into the goal.</t>
+  </si>
+  <si>
+    <t>89:36</t>
+  </si>
+  <si>
+    <t>Us</t>
+  </si>
+  <si>
+    <t>Driven</t>
+  </si>
+  <si>
+    <t>Right Channel</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>GK Right</t>
+  </si>
+  <si>
+    <t>Red team player dekes around the defender outside of the top of the 18 yard box on the right. Drives a low hard short to the opposite post to beat the GK.</t>
+  </si>
+  <si>
+    <t>GK is set, moves in the right direction but ball goes under her hands as she attempts a low dive/collapse</t>
+  </si>
+  <si>
     <t>Shot origin</t>
   </si>
   <si>
@@ -239,6 +308,69 @@
     <t>Body zone (A/B/C)</t>
   </si>
   <si>
+    <t>45:21</t>
+  </si>
+  <si>
+    <t>Foot</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Smother</t>
+  </si>
+  <si>
+    <t>Held</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Centre</t>
+  </si>
+  <si>
+    <t>Defender clearance to the top of the box after a corner. Blue player takes a touch before shooting through the crowd directly on net and directly at the GK.</t>
+  </si>
+  <si>
+    <t>GK hesitates to go claim the corner, defender clears into danger. Keeper is on their toes ready and set. Collects ball easily.</t>
+  </si>
+  <si>
+    <t>61:59</t>
+  </si>
+  <si>
+    <t>Player coming down the wing shoots (maybe a cross attempt) on goal, nearside. GK is ready and smothers the ball.</t>
+  </si>
+  <si>
+    <t>GK set and ready. Makes a routine scoop/smother save.</t>
+  </si>
+  <si>
+    <t>71:09</t>
+  </si>
+  <si>
+    <t>Left Channel</t>
+  </si>
+  <si>
+    <t>Catch</t>
+  </si>
+  <si>
+    <t>Opponent volleys a high looping shot from the left side of the 18 yard box on goal.</t>
+  </si>
+  <si>
+    <t>GK is set, back pedals well to jump and make the save high above her head.</t>
+  </si>
+  <si>
+    <t>102:37</t>
+  </si>
+  <si>
+    <t>Central Distance</t>
+  </si>
+  <si>
+    <t>Player misses a pass up the middle, loose ball picked up by the GK at the 6 yard box.</t>
+  </si>
+  <si>
+    <t>Set. Ready. Easy pick up from a missed pass up the middle.</t>
+  </si>
+  <si>
     <t>QUICK TOTALS — fill these IN PLACE OF logging every event if you do not want to tag row-by-row.</t>
   </si>
   <si>
@@ -297,6 +429,171 @@
   </si>
   <si>
     <t>First touch</t>
+  </si>
+  <si>
+    <t>35:34</t>
+  </si>
+  <si>
+    <t>Goal kick</t>
+  </si>
+  <si>
+    <t>GK Short Kick</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Short to defender</t>
+  </si>
+  <si>
+    <t>Right</t>
+  </si>
+  <si>
+    <t>Defender</t>
+  </si>
+  <si>
+    <t>Clean</t>
+  </si>
+  <si>
+    <t>36:32</t>
+  </si>
+  <si>
+    <t>Backpass</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>36:39</t>
+  </si>
+  <si>
+    <t>41:46</t>
+  </si>
+  <si>
+    <t>Left</t>
+  </si>
+  <si>
+    <t>45:29</t>
+  </si>
+  <si>
+    <t>After save</t>
+  </si>
+  <si>
+    <t>Drop-kick</t>
+  </si>
+  <si>
+    <t>Long to forward</t>
+  </si>
+  <si>
+    <t>Midfielder</t>
+  </si>
+  <si>
+    <t>Heavy</t>
+  </si>
+  <si>
+    <t>Loss of possession. Drop-kick was to an opponent near half-field</t>
+  </si>
+  <si>
+    <t>51:03</t>
+  </si>
+  <si>
+    <t>56:50</t>
+  </si>
+  <si>
+    <t>Loose ball in box</t>
+  </si>
+  <si>
+    <t>Throw</t>
+  </si>
+  <si>
+    <t>Sideways across back</t>
+  </si>
+  <si>
+    <t>60:04</t>
+  </si>
+  <si>
+    <t>60:15</t>
+  </si>
+  <si>
+    <t>61:28</t>
+  </si>
+  <si>
+    <t>61:36</t>
+  </si>
+  <si>
+    <t>62:03</t>
+  </si>
+  <si>
+    <t>62:29</t>
+  </si>
+  <si>
+    <t>62:35</t>
+  </si>
+  <si>
+    <t>64:18</t>
+  </si>
+  <si>
+    <t>70:46</t>
+  </si>
+  <si>
+    <t>71:15</t>
+  </si>
+  <si>
+    <t>71:20</t>
+  </si>
+  <si>
+    <t>93:14</t>
+  </si>
+  <si>
+    <t>93:17</t>
+  </si>
+  <si>
+    <t>96:51</t>
+  </si>
+  <si>
+    <t>97:00</t>
+  </si>
+  <si>
+    <t>99:18</t>
+  </si>
+  <si>
+    <t>99:29</t>
+  </si>
+  <si>
+    <t>101:53</t>
+  </si>
+  <si>
+    <t>102:20</t>
+  </si>
+  <si>
+    <t>102:42</t>
+  </si>
+  <si>
+    <t>102:53</t>
+  </si>
+  <si>
+    <t>106:19</t>
+  </si>
+  <si>
+    <t>107:03</t>
+  </si>
+  <si>
+    <t>107:45</t>
+  </si>
+  <si>
+    <t>108:04</t>
+  </si>
+  <si>
+    <t>110:38</t>
+  </si>
+  <si>
+    <t>112:29</t>
+  </si>
+  <si>
+    <t>114:40</t>
+  </si>
+  <si>
+    <t>116:20</t>
   </si>
   <si>
     <t>Side</t>
@@ -338,23 +635,32 @@
     <font>
       <b/>
       <sz val="16"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <color rgb="FF333333"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <i/>
       <color rgb="FF666666"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -364,6 +670,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1E2A32"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -388,7 +700,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -397,7 +709,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -741,12 +1055,12 @@
     <tabColor rgb="FF888888"/>
   </sheetPr>
   <dimension ref="A1:A32"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" ht="21" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -917,8 +1231,8 @@
   <sheetPr>
     <tabColor rgb="FF666666"/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
@@ -951,7 +1265,7 @@
       <c r="A3" t="s">
         <v>34</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C3" t="s">
@@ -990,74 +1304,90 @@
         <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B10" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
+      </c>
+      <c r="B11" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" t="s">
-        <v>56</v>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="B10">
+    <dataValidation type="list" allowBlank="1" sqref="B12">
       <formula1>"U6,U7,U8,U9,U10,U11,U12,U13,U14,U15,U16,U17,U18,Senior"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B5">
@@ -1078,7 +1408,7 @@
     <tabColor rgb="FFEF4444"/>
   </sheetPr>
   <dimension ref="A1:K202"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -1092,44 +1422,99 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J3" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
@@ -1784,7 +2169,7 @@
     <tabColor rgb="FF10B981"/>
   </sheetPr>
   <dimension ref="A1:N202"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -1801,59 +2186,211 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>65</v>
-      </c>
       <c r="M1" s="4" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="N1" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J2" t="s">
+        <v>85</v>
+      </c>
+      <c r="K2" t="s">
+        <v>101</v>
+      </c>
+      <c r="L2" t="s">
+        <v>102</v>
+      </c>
+      <c r="M2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3" t="s">
+        <v>99</v>
+      </c>
+      <c r="I3" t="s">
+        <v>100</v>
+      </c>
+      <c r="J3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K3" t="s">
+        <v>79</v>
+      </c>
+      <c r="L3" t="s">
+        <v>105</v>
+      </c>
+      <c r="M3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I4" t="s">
+        <v>100</v>
+      </c>
+      <c r="J4" t="s">
+        <v>78</v>
+      </c>
+      <c r="K4" t="s">
+        <v>101</v>
+      </c>
+      <c r="L4" t="s">
+        <v>110</v>
+      </c>
+      <c r="M4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I5" t="s">
+        <v>100</v>
+      </c>
+      <c r="J5" t="s">
+        <v>85</v>
+      </c>
+      <c r="K5" t="s">
+        <v>101</v>
+      </c>
+      <c r="L5" t="s">
+        <v>114</v>
+      </c>
+      <c r="M5" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
@@ -2520,9 +3057,9 @@
     <tabColor rgb="FF3B82F6"/>
   </sheetPr>
   <dimension ref="A1:K217"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
@@ -2536,100 +3073,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
+      <c r="A1" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+    </row>
+    <row r="4" hidden="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>75</v>
+        <v>118</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" hidden="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" hidden="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" hidden="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" hidden="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" hidden="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="B9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" hidden="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="B10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" hidden="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="B11" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" hidden="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" hidden="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="B13" t="s">
         <v>1</v>
@@ -2637,146 +3174,1193 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>87</v>
+        <v>130</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>89</v>
+        <v>132</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>90</v>
+        <v>133</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="5"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="5"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="5"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="5"/>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="5"/>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="5"/>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="5"/>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="5"/>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="5"/>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="5"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="5"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="5"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="5"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="5"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="5"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="5"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="5"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="5"/>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="5"/>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="5"/>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="5"/>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="5"/>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="5"/>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="5"/>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="5"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="5"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="5"/>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="5"/>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="5"/>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>137</v>
+      </c>
+      <c r="D17" t="s">
+        <v>138</v>
+      </c>
+      <c r="E17" t="s">
+        <v>97</v>
+      </c>
+      <c r="F17" t="s">
+        <v>139</v>
+      </c>
+      <c r="G17" t="s">
+        <v>140</v>
+      </c>
+      <c r="H17" t="s">
+        <v>141</v>
+      </c>
+      <c r="I17" t="s">
+        <v>142</v>
+      </c>
+      <c r="J17" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>145</v>
+      </c>
+      <c r="D18" t="s">
+        <v>146</v>
+      </c>
+      <c r="E18" t="s">
+        <v>97</v>
+      </c>
+      <c r="F18" t="s">
+        <v>139</v>
+      </c>
+      <c r="G18" t="s">
+        <v>140</v>
+      </c>
+      <c r="H18" t="s">
+        <v>141</v>
+      </c>
+      <c r="I18" t="s">
+        <v>142</v>
+      </c>
+      <c r="J18" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>145</v>
+      </c>
+      <c r="D19" t="s">
+        <v>146</v>
+      </c>
+      <c r="E19" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19" t="s">
+        <v>139</v>
+      </c>
+      <c r="G19" t="s">
+        <v>140</v>
+      </c>
+      <c r="H19" t="s">
+        <v>141</v>
+      </c>
+      <c r="I19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J19" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>145</v>
+      </c>
+      <c r="D20" t="s">
+        <v>146</v>
+      </c>
+      <c r="E20" t="s">
+        <v>97</v>
+      </c>
+      <c r="F20" t="s">
+        <v>139</v>
+      </c>
+      <c r="G20" t="s">
+        <v>140</v>
+      </c>
+      <c r="H20" t="s">
+        <v>149</v>
+      </c>
+      <c r="I20" t="s">
+        <v>142</v>
+      </c>
+      <c r="J20" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>151</v>
+      </c>
+      <c r="D21" t="s">
+        <v>152</v>
+      </c>
+      <c r="E21" t="s">
+        <v>139</v>
+      </c>
+      <c r="F21" t="s">
+        <v>139</v>
+      </c>
+      <c r="G21" t="s">
+        <v>153</v>
+      </c>
+      <c r="H21" t="s">
+        <v>101</v>
+      </c>
+      <c r="I21" t="s">
+        <v>154</v>
+      </c>
+      <c r="J21" t="s">
+        <v>155</v>
+      </c>
+      <c r="K21" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>145</v>
+      </c>
+      <c r="D22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E22" t="s">
+        <v>97</v>
+      </c>
+      <c r="F22" t="s">
+        <v>139</v>
+      </c>
+      <c r="G22" t="s">
+        <v>140</v>
+      </c>
+      <c r="H22" t="s">
+        <v>141</v>
+      </c>
+      <c r="I22" t="s">
+        <v>142</v>
+      </c>
+      <c r="J22" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
+        <v>159</v>
+      </c>
+      <c r="D23" t="s">
+        <v>160</v>
+      </c>
+      <c r="E23" t="s">
+        <v>97</v>
+      </c>
+      <c r="F23" t="s">
+        <v>139</v>
+      </c>
+      <c r="G23" t="s">
+        <v>161</v>
+      </c>
+      <c r="H23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I23" t="s">
+        <v>142</v>
+      </c>
+      <c r="J23" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>137</v>
+      </c>
+      <c r="D24" t="s">
+        <v>138</v>
+      </c>
+      <c r="E24" t="s">
+        <v>97</v>
+      </c>
+      <c r="F24" t="s">
+        <v>139</v>
+      </c>
+      <c r="G24" t="s">
+        <v>140</v>
+      </c>
+      <c r="H24" t="s">
+        <v>141</v>
+      </c>
+      <c r="I24" t="s">
+        <v>142</v>
+      </c>
+      <c r="J24" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>145</v>
+      </c>
+      <c r="D25" t="s">
+        <v>146</v>
+      </c>
+      <c r="E25" t="s">
+        <v>97</v>
+      </c>
+      <c r="F25" t="s">
+        <v>139</v>
+      </c>
+      <c r="G25" t="s">
+        <v>161</v>
+      </c>
+      <c r="H25" t="s">
+        <v>149</v>
+      </c>
+      <c r="I25" t="s">
+        <v>142</v>
+      </c>
+      <c r="J25" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" t="s">
+        <v>138</v>
+      </c>
+      <c r="E26" t="s">
+        <v>97</v>
+      </c>
+      <c r="F26" t="s">
+        <v>139</v>
+      </c>
+      <c r="G26" t="s">
+        <v>140</v>
+      </c>
+      <c r="H26" t="s">
+        <v>141</v>
+      </c>
+      <c r="I26" t="s">
+        <v>142</v>
+      </c>
+      <c r="J26" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
+        <v>145</v>
+      </c>
+      <c r="D27" t="s">
+        <v>146</v>
+      </c>
+      <c r="E27" t="s">
+        <v>97</v>
+      </c>
+      <c r="F27" t="s">
+        <v>139</v>
+      </c>
+      <c r="G27" t="s">
+        <v>161</v>
+      </c>
+      <c r="H27" t="s">
+        <v>149</v>
+      </c>
+      <c r="I27" t="s">
+        <v>142</v>
+      </c>
+      <c r="J27" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>151</v>
+      </c>
+      <c r="D28" t="s">
+        <v>160</v>
+      </c>
+      <c r="E28" t="s">
+        <v>97</v>
+      </c>
+      <c r="F28" t="s">
+        <v>139</v>
+      </c>
+      <c r="G28" t="s">
+        <v>161</v>
+      </c>
+      <c r="H28" t="s">
+        <v>141</v>
+      </c>
+      <c r="I28" t="s">
+        <v>142</v>
+      </c>
+      <c r="J28" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>145</v>
+      </c>
+      <c r="D29" t="s">
+        <v>146</v>
+      </c>
+      <c r="E29" t="s">
+        <v>97</v>
+      </c>
+      <c r="F29" t="s">
+        <v>139</v>
+      </c>
+      <c r="G29" t="s">
+        <v>140</v>
+      </c>
+      <c r="H29" t="s">
+        <v>141</v>
+      </c>
+      <c r="I29" t="s">
+        <v>142</v>
+      </c>
+      <c r="J29" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>145</v>
+      </c>
+      <c r="D30" t="s">
+        <v>146</v>
+      </c>
+      <c r="E30" t="s">
+        <v>97</v>
+      </c>
+      <c r="F30" t="s">
+        <v>139</v>
+      </c>
+      <c r="G30" t="s">
+        <v>161</v>
+      </c>
+      <c r="H30" t="s">
+        <v>141</v>
+      </c>
+      <c r="I30" t="s">
+        <v>142</v>
+      </c>
+      <c r="J30" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
+        <v>137</v>
+      </c>
+      <c r="D31" t="s">
+        <v>138</v>
+      </c>
+      <c r="E31" t="s">
+        <v>97</v>
+      </c>
+      <c r="F31" t="s">
+        <v>139</v>
+      </c>
+      <c r="G31" t="s">
+        <v>140</v>
+      </c>
+      <c r="H31" t="s">
+        <v>149</v>
+      </c>
+      <c r="I31" t="s">
+        <v>142</v>
+      </c>
+      <c r="J31" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>137</v>
+      </c>
+      <c r="D32" t="s">
+        <v>138</v>
+      </c>
+      <c r="E32" t="s">
+        <v>97</v>
+      </c>
+      <c r="F32" t="s">
+        <v>139</v>
+      </c>
+      <c r="G32" t="s">
+        <v>140</v>
+      </c>
+      <c r="H32" t="s">
+        <v>149</v>
+      </c>
+      <c r="I32" t="s">
+        <v>142</v>
+      </c>
+      <c r="J32" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>151</v>
+      </c>
+      <c r="D33" t="s">
+        <v>160</v>
+      </c>
+      <c r="E33" t="s">
+        <v>97</v>
+      </c>
+      <c r="F33" t="s">
+        <v>139</v>
+      </c>
+      <c r="G33" t="s">
+        <v>140</v>
+      </c>
+      <c r="H33" t="s">
+        <v>141</v>
+      </c>
+      <c r="I33" t="s">
+        <v>142</v>
+      </c>
+      <c r="J33" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
+        <v>145</v>
+      </c>
+      <c r="D34" t="s">
+        <v>146</v>
+      </c>
+      <c r="E34" t="s">
+        <v>97</v>
+      </c>
+      <c r="F34" t="s">
+        <v>139</v>
+      </c>
+      <c r="G34" t="s">
+        <v>161</v>
+      </c>
+      <c r="H34" t="s">
+        <v>149</v>
+      </c>
+      <c r="I34" t="s">
+        <v>142</v>
+      </c>
+      <c r="J34" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="B35">
+        <v>2</v>
+      </c>
+      <c r="C35" t="s">
+        <v>137</v>
+      </c>
+      <c r="D35" t="s">
+        <v>138</v>
+      </c>
+      <c r="E35" t="s">
+        <v>97</v>
+      </c>
+      <c r="F35" t="s">
+        <v>139</v>
+      </c>
+      <c r="G35" t="s">
+        <v>140</v>
+      </c>
+      <c r="H35" t="s">
+        <v>149</v>
+      </c>
+      <c r="I35" t="s">
+        <v>142</v>
+      </c>
+      <c r="J35" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B36">
+        <v>2</v>
+      </c>
+      <c r="C36" t="s">
+        <v>145</v>
+      </c>
+      <c r="D36" t="s">
+        <v>146</v>
+      </c>
+      <c r="E36" t="s">
+        <v>97</v>
+      </c>
+      <c r="F36" t="s">
+        <v>139</v>
+      </c>
+      <c r="G36" t="s">
+        <v>161</v>
+      </c>
+      <c r="H36" t="s">
+        <v>141</v>
+      </c>
+      <c r="I36" t="s">
+        <v>142</v>
+      </c>
+      <c r="J36" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B37">
+        <v>2</v>
+      </c>
+      <c r="C37" t="s">
+        <v>145</v>
+      </c>
+      <c r="D37" t="s">
+        <v>146</v>
+      </c>
+      <c r="E37" t="s">
+        <v>97</v>
+      </c>
+      <c r="F37" t="s">
+        <v>139</v>
+      </c>
+      <c r="G37" t="s">
+        <v>161</v>
+      </c>
+      <c r="H37" t="s">
+        <v>149</v>
+      </c>
+      <c r="I37" t="s">
+        <v>142</v>
+      </c>
+      <c r="J37" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B38">
+        <v>2</v>
+      </c>
+      <c r="C38" t="s">
+        <v>145</v>
+      </c>
+      <c r="D38" t="s">
+        <v>146</v>
+      </c>
+      <c r="E38" t="s">
+        <v>97</v>
+      </c>
+      <c r="F38" t="s">
+        <v>139</v>
+      </c>
+      <c r="G38" t="s">
+        <v>161</v>
+      </c>
+      <c r="H38" t="s">
+        <v>141</v>
+      </c>
+      <c r="I38" t="s">
+        <v>142</v>
+      </c>
+      <c r="J38" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="B39">
+        <v>2</v>
+      </c>
+      <c r="C39" t="s">
+        <v>137</v>
+      </c>
+      <c r="D39" t="s">
+        <v>138</v>
+      </c>
+      <c r="E39" t="s">
+        <v>97</v>
+      </c>
+      <c r="F39" t="s">
+        <v>139</v>
+      </c>
+      <c r="G39" t="s">
+        <v>140</v>
+      </c>
+      <c r="H39" t="s">
+        <v>149</v>
+      </c>
+      <c r="I39" t="s">
+        <v>142</v>
+      </c>
+      <c r="J39" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B40">
+        <v>2</v>
+      </c>
+      <c r="C40" t="s">
+        <v>137</v>
+      </c>
+      <c r="D40" t="s">
+        <v>138</v>
+      </c>
+      <c r="E40" t="s">
+        <v>97</v>
+      </c>
+      <c r="F40" t="s">
+        <v>139</v>
+      </c>
+      <c r="G40" t="s">
+        <v>140</v>
+      </c>
+      <c r="H40" t="s">
+        <v>149</v>
+      </c>
+      <c r="I40" t="s">
+        <v>142</v>
+      </c>
+      <c r="J40" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B41">
+        <v>2</v>
+      </c>
+      <c r="C41" t="s">
+        <v>145</v>
+      </c>
+      <c r="D41" t="s">
+        <v>146</v>
+      </c>
+      <c r="E41" t="s">
+        <v>97</v>
+      </c>
+      <c r="F41" t="s">
+        <v>139</v>
+      </c>
+      <c r="G41" t="s">
+        <v>161</v>
+      </c>
+      <c r="H41" t="s">
+        <v>141</v>
+      </c>
+      <c r="I41" t="s">
+        <v>142</v>
+      </c>
+      <c r="J41" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="B42">
+        <v>2</v>
+      </c>
+      <c r="C42" t="s">
+        <v>145</v>
+      </c>
+      <c r="D42" t="s">
+        <v>146</v>
+      </c>
+      <c r="E42" t="s">
+        <v>97</v>
+      </c>
+      <c r="F42" t="s">
+        <v>139</v>
+      </c>
+      <c r="G42" t="s">
+        <v>153</v>
+      </c>
+      <c r="H42" t="s">
+        <v>101</v>
+      </c>
+      <c r="I42" t="s">
+        <v>154</v>
+      </c>
+      <c r="J42" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B43">
+        <v>2</v>
+      </c>
+      <c r="C43" t="s">
+        <v>151</v>
+      </c>
+      <c r="D43" t="s">
+        <v>160</v>
+      </c>
+      <c r="E43" t="s">
+        <v>97</v>
+      </c>
+      <c r="F43" t="s">
+        <v>139</v>
+      </c>
+      <c r="G43" t="s">
+        <v>140</v>
+      </c>
+      <c r="H43" t="s">
+        <v>149</v>
+      </c>
+      <c r="I43" t="s">
+        <v>142</v>
+      </c>
+      <c r="J43" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="B44">
+        <v>2</v>
+      </c>
+      <c r="C44" t="s">
+        <v>145</v>
+      </c>
+      <c r="D44" t="s">
+        <v>146</v>
+      </c>
+      <c r="E44" t="s">
+        <v>97</v>
+      </c>
+      <c r="F44" t="s">
+        <v>139</v>
+      </c>
+      <c r="G44" t="s">
+        <v>161</v>
+      </c>
+      <c r="H44" t="s">
+        <v>141</v>
+      </c>
+      <c r="I44" t="s">
+        <v>142</v>
+      </c>
+      <c r="J44" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B45">
+        <v>2</v>
+      </c>
+      <c r="C45" t="s">
+        <v>137</v>
+      </c>
+      <c r="D45" t="s">
+        <v>138</v>
+      </c>
+      <c r="E45" t="s">
+        <v>97</v>
+      </c>
+      <c r="F45" t="s">
+        <v>139</v>
+      </c>
+      <c r="G45" t="s">
+        <v>140</v>
+      </c>
+      <c r="H45" t="s">
+        <v>141</v>
+      </c>
+      <c r="I45" t="s">
+        <v>142</v>
+      </c>
+      <c r="J45" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B46">
+        <v>2</v>
+      </c>
+      <c r="C46" t="s">
+        <v>137</v>
+      </c>
+      <c r="D46" t="s">
+        <v>138</v>
+      </c>
+      <c r="E46" t="s">
+        <v>97</v>
+      </c>
+      <c r="F46" t="s">
+        <v>139</v>
+      </c>
+      <c r="G46" t="s">
+        <v>140</v>
+      </c>
+      <c r="H46" t="s">
+        <v>149</v>
+      </c>
+      <c r="I46" t="s">
+        <v>142</v>
+      </c>
+      <c r="J46" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B47">
+        <v>2</v>
+      </c>
+      <c r="C47" t="s">
+        <v>137</v>
+      </c>
+      <c r="D47" t="s">
+        <v>138</v>
+      </c>
+      <c r="E47" t="s">
+        <v>97</v>
+      </c>
+      <c r="F47" t="s">
+        <v>139</v>
+      </c>
+      <c r="G47" t="s">
+        <v>140</v>
+      </c>
+      <c r="H47" t="s">
+        <v>141</v>
+      </c>
+      <c r="I47" t="s">
+        <v>142</v>
+      </c>
+      <c r="J47" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="B48">
+        <v>2</v>
+      </c>
+      <c r="C48" t="s">
+        <v>145</v>
+      </c>
+      <c r="D48" t="s">
+        <v>146</v>
+      </c>
+      <c r="E48" t="s">
+        <v>97</v>
+      </c>
+      <c r="F48" t="s">
+        <v>139</v>
+      </c>
+      <c r="G48" t="s">
+        <v>161</v>
+      </c>
+      <c r="H48" t="s">
+        <v>141</v>
+      </c>
+      <c r="I48" t="s">
+        <v>142</v>
+      </c>
+      <c r="J48" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B49">
+        <v>2</v>
+      </c>
+      <c r="C49" t="s">
+        <v>137</v>
+      </c>
+      <c r="D49" t="s">
+        <v>138</v>
+      </c>
+      <c r="E49" t="s">
+        <v>97</v>
+      </c>
+      <c r="F49" t="s">
+        <v>139</v>
+      </c>
+      <c r="G49" t="s">
+        <v>140</v>
+      </c>
+      <c r="H49" t="s">
+        <v>141</v>
+      </c>
+      <c r="I49" t="s">
+        <v>142</v>
+      </c>
+      <c r="J49" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="B50">
+        <v>2</v>
+      </c>
+      <c r="C50" t="s">
+        <v>145</v>
+      </c>
+      <c r="D50" t="s">
+        <v>146</v>
+      </c>
+      <c r="E50" t="s">
+        <v>97</v>
+      </c>
+      <c r="F50" t="s">
+        <v>139</v>
+      </c>
+      <c r="G50" t="s">
+        <v>161</v>
+      </c>
+      <c r="H50" t="s">
+        <v>141</v>
+      </c>
+      <c r="I50" t="s">
+        <v>142</v>
+      </c>
+      <c r="J50" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B51">
+        <v>2</v>
+      </c>
+      <c r="C51" t="s">
+        <v>137</v>
+      </c>
+      <c r="D51" t="s">
+        <v>138</v>
+      </c>
+      <c r="E51" t="s">
+        <v>97</v>
+      </c>
+      <c r="F51" t="s">
+        <v>139</v>
+      </c>
+      <c r="G51" t="s">
+        <v>140</v>
+      </c>
+      <c r="H51" t="s">
+        <v>141</v>
+      </c>
+      <c r="I51" t="s">
+        <v>142</v>
+      </c>
+      <c r="J51" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B52">
+        <v>2</v>
+      </c>
+      <c r="C52" t="s">
+        <v>137</v>
+      </c>
+      <c r="D52" t="s">
+        <v>138</v>
+      </c>
+      <c r="E52" t="s">
+        <v>97</v>
+      </c>
+      <c r="F52" t="s">
+        <v>139</v>
+      </c>
+      <c r="G52" t="s">
+        <v>140</v>
+      </c>
+      <c r="H52" t="s">
+        <v>141</v>
+      </c>
+      <c r="I52" t="s">
+        <v>142</v>
+      </c>
+      <c r="J52" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
@@ -3339,7 +4923,7 @@
     <tabColor rgb="FFF97316"/>
   </sheetPr>
   <dimension ref="A1:I202"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -3352,28 +4936,28 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>71</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>30</v>
@@ -4038,7 +5622,7 @@
     <tabColor rgb="FFA78BFA"/>
   </sheetPr>
   <dimension ref="A1:H202"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -4052,25 +5636,25 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>97</v>
+        <v>195</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>98</v>
+        <v>196</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>87</v>
+        <v>130</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>99</v>
+        <v>197</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>30</v>
@@ -4729,7 +6313,7 @@
     <tabColor rgb="FFD4A853"/>
   </sheetPr>
   <dimension ref="A1:E202"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -4740,16 +6324,16 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>100</v>
+        <v>198</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>30</v>
